--- a/data/source/player_wages.xlsx
+++ b/data/source/player_wages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\Desktop\ID-PROJ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\Documents\AltairRapidMiner\AI Studio\Repositories\IDProj\data\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECAA3724-CD4B-4B7B-A2C3-4254ED988600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73BFD40-CC84-492C-8057-3C75EF70CF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C8B6D63-B4B5-4D60-B3A0-BA0B93FBC0DA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6C8B6D63-B4B5-4D60-B3A0-BA0B93FBC0DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="129">
   <si>
     <t>Player</t>
   </si>
@@ -449,23 +449,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Aptos Display"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8.6"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="2">
@@ -489,24 +491,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hiperligação" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -523,7 +526,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -840,1002 +843,1027 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{123947A9-2064-46D7-BACC-BD3235A2F2B4}">
   <dimension ref="A1:J43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="28.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.6640625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="28.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.7109375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1">
+        <v>51</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="6">
+        <v>27</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1">
-        <v>30</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D3" s="6">
+        <v>23</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1">
-        <v>25</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="6">
+        <v>29</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1">
-        <v>32</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D5" s="6">
+        <v>18</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="1">
-        <v>26</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="6">
+        <v>22</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="1">
-        <v>22</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="6">
+        <v>30</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="6">
         <v>25</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="6">
+        <v>33</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="6">
+        <v>17</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="C11" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="6">
+        <v>20</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="6">
+        <v>18</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="6">
         <v>26</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="J9" s="5"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="E13" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="6">
+        <v>19</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="1">
-        <v>30</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="1">
-        <v>27</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="1" t="s">
+      <c r="C15" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="6">
+        <v>20</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="1">
-        <v>27</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="1">
-        <v>23</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="1">
-        <v>24</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G14" s="1" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="6">
+        <v>19</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="6">
+        <v>19</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="1">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="6">
         <v>19</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="1">
-        <v>24</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="1">
-        <v>26</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="E18" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="1">
-        <v>25</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="1">
-        <v>23</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="6">
+        <v>18</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="6">
+        <v>32</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="6">
+        <v>19</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D22" s="6">
         <v>25</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E22" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F22" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="1">
+      <c r="C23" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="6">
+        <v>21</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="1">
-        <v>20</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="1">
-        <v>27</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D24" s="6">
+        <v>24</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="6">
+        <v>20</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="1">
-        <v>20</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="1">
-        <v>20</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D26" s="6">
+        <v>19</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="1">
-        <v>18</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D27" s="6">
+        <v>27</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="1">
-        <v>18</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G28" s="1" t="s">
+      <c r="D28" s="6">
+        <v>30</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="6">
+        <v>24</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29" s="1">
-        <v>17</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="1">
-        <v>19</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C30" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="6">
+        <v>27</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G30" s="6"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D31" s="1">
+      <c r="C31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="6">
+        <v>26</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G31" s="6"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="6">
+        <v>26</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" s="6"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="6">
+        <v>25</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="6">
+        <v>27</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="6">
+        <v>20</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="6">
         <v>21</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G31" s="1" t="s">
+      <c r="E37" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="1">
-        <v>20</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G32" s="1" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="6">
+        <v>23</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="1">
-        <v>21</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="1">
-        <v>19</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D35" s="1">
-        <v>20</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="1">
-        <v>19</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D37" s="1">
-        <v>19</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D38" s="1">
-        <v>20</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D39" s="1">
-        <v>18</v>
-      </c>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C39" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D39" s="6">
+        <v>20</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" s="1">
-        <v>27</v>
-      </c>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C40" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="6">
+        <v>21</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="1">
-        <v>29</v>
-      </c>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D41" s="6">
+        <v>39</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" s="1">
-        <v>21</v>
-      </c>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D43" s="1">
-        <v>19</v>
-      </c>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="3"/>
+      <c r="C42" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="6">
+        <v>20</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="6">
+        <v>25</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{123947A9-2064-46D7-BACC-BD3235A2F2B4}"/>
+  <autoFilter ref="A1:G1" xr:uid="{123947A9-2064-46D7-BACC-BD3235A2F2B4}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G43">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B42" r:id="rId1" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{3F72A3A5-56D5-4954-A3B6-79E42E30285A}"/>
-    <hyperlink ref="A42" r:id="rId2" display="https://fbref.com/en/players/4f9091bc/Toby-Collyer" xr:uid="{A49984C9-035D-4ED7-BFF6-BFE428753D7F}"/>
-    <hyperlink ref="B41" r:id="rId3" display="https://fbref.com/en/country/CMR/Cameroon-Football" xr:uid="{496DBF89-955E-4872-BCBA-F5EE8E0CFA31}"/>
-    <hyperlink ref="A41" r:id="rId4" display="https://fbref.com/en/players/e9c0c1b2/Andre-Onana" xr:uid="{B0DC6747-5F67-4934-9613-EFFC5261C988}"/>
-    <hyperlink ref="B40" r:id="rId5" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{18F8EE63-3D84-444A-A684-F2A4B8F452AD}"/>
-    <hyperlink ref="A40" r:id="rId6" display="https://fbref.com/en/players/a1d5bd30/Marcus-Rashford" xr:uid="{4387A829-7F2B-4395-94F1-47D9693B53CF}"/>
-    <hyperlink ref="B39" r:id="rId7" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{A7EA4D34-C7D8-4C15-86F7-4E2B6F7ED264}"/>
-    <hyperlink ref="A39" r:id="rId8" display="https://fbref.com/en/players/7b47100c/Harry-Amass" xr:uid="{16EC9CB6-7073-4E09-9636-60F62D7A7595}"/>
-    <hyperlink ref="B38" r:id="rId9" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{DCE8B9BB-FE67-450A-83BD-1A97C48E6EE7}"/>
-    <hyperlink ref="A38" r:id="rId10" display="https://fbref.com/en/players/bd44b52f/Sonny-Aljofree" xr:uid="{2E48A29F-E35A-4703-B9FD-975687D6CFB7}"/>
-    <hyperlink ref="B36" r:id="rId11" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{69C9EBA4-D0BB-44AC-82D3-709623309A9C}"/>
-    <hyperlink ref="A36" r:id="rId12" display="https://fbref.com/en/players/d8b9fc76/Ethan-Williams" xr:uid="{DA7EF6BC-C7AC-4146-B1B8-6AE08787FC89}"/>
-    <hyperlink ref="B35" r:id="rId13" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{5F48DF20-2424-4775-ADE4-2B30EB0DAE10}"/>
-    <hyperlink ref="A35" r:id="rId14" display="https://fbref.com/en/players/143c022e/Ethan-Ennis" xr:uid="{4D8969FB-1D99-4603-B985-E5D207499BFD}"/>
-    <hyperlink ref="B32" r:id="rId15" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{DC2E306B-DEC4-48E9-BBF1-723524E42336}"/>
-    <hyperlink ref="A32" r:id="rId16" display="https://fbref.com/en/players/861e9b3b/Daniel-Gore" xr:uid="{CB57EFD9-7A1C-41EF-A987-F9FB26B92EFE}"/>
-    <hyperlink ref="B31" r:id="rId17" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{7C586973-16AD-4C72-9884-57741421A443}"/>
-    <hyperlink ref="A31" r:id="rId18" display="https://fbref.com/en/players/49134eb2/Joe-Hugill" xr:uid="{3C942A50-F930-4DD0-8A46-0C2E809C2F0F}"/>
-    <hyperlink ref="B30" r:id="rId19" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{012BBF0E-852F-4F07-B5FE-E5F4F9A01540}"/>
-    <hyperlink ref="A30" r:id="rId20" display="https://fbref.com/en/players/5c368c88/Ethan-Wheatley" xr:uid="{719D3E7A-0F8B-40B8-A619-322E65470979}"/>
-    <hyperlink ref="B28" r:id="rId21" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{B74F1AB9-E89D-4E44-963E-E84DFF3C72BD}"/>
-    <hyperlink ref="A28" r:id="rId22" display="https://fbref.com/en/players/64e17fab/Ayden-Heaven" xr:uid="{3D62F65F-9B0E-48B1-8DDE-47E8DC4D5CEA}"/>
-    <hyperlink ref="B27" r:id="rId23" display="https://fbref.com/en/country/PAR/Paraguay-Football" xr:uid="{BD610C72-90D7-40EB-BA7B-F74E512D8055}"/>
-    <hyperlink ref="A27" r:id="rId24" display="https://fbref.com/en/players/69ea448b/Diego-Leon" xr:uid="{34675B85-5D48-4A26-8D69-43557513254D}"/>
-    <hyperlink ref="B26" r:id="rId25" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{101CC625-E8F0-4A2B-BFC2-428D67523A16}"/>
-    <hyperlink ref="A26" r:id="rId26" display="https://fbref.com/en/players/c6220452/Kobbie-Mainoo" xr:uid="{900AD290-779C-4561-B227-678075E6BE40}"/>
-    <hyperlink ref="B25" r:id="rId27" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{DB680947-0EAF-45F3-9672-5D601742FD66}"/>
-    <hyperlink ref="A25" r:id="rId28" display="https://fbref.com/en/players/58630379/Tyler-Fredricson" xr:uid="{5AB50ECA-C52B-40B8-A4BF-DA7132708977}"/>
-    <hyperlink ref="B24" r:id="rId29" display="https://fbref.com/en/country/TUR/Turkey-Football" xr:uid="{A8C90F14-F1C0-4BAC-9340-B609C66F83B2}"/>
-    <hyperlink ref="A24" r:id="rId30" display="https://fbref.com/en/players/072e68ed/Altay-Bayindir" xr:uid="{72C7336C-0146-4005-894A-1F89BE49A78C}"/>
-    <hyperlink ref="B23" r:id="rId31" display="https://fbref.com/en/country/DEN/Denmark-Football" xr:uid="{47496AF9-C9F4-4992-9A46-7155209E3CE2}"/>
-    <hyperlink ref="A23" r:id="rId32" display="https://fbref.com/en/players/e6536124/Patrick-Dorgu" xr:uid="{B2CC8187-60D3-409C-82D0-E3E7E78A4906}"/>
-    <hyperlink ref="B21" r:id="rId33" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{7276AEB2-71E9-42BF-8FB5-BB2020CBE4DC}"/>
-    <hyperlink ref="A21" r:id="rId34" display="https://fbref.com/en/players/a6de6361/Tom-Heaton" xr:uid="{C2F55E8B-E7DB-449C-BE43-4E78713600E0}"/>
-    <hyperlink ref="B20" r:id="rId35" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{87ACC8BC-A024-4CBE-9E17-DC7148F7015B}"/>
-    <hyperlink ref="A20" r:id="rId36" display="https://fbref.com/en/players/dbf053da/Jadon-Sancho" xr:uid="{3833287A-E4EB-4527-9D74-09662B51D4CD}"/>
-    <hyperlink ref="B19" r:id="rId37" display="https://fbref.com/en/country/BEL/Belgium-Football" xr:uid="{0F4D7669-FF1D-42E1-914C-43726D0939FA}"/>
-    <hyperlink ref="A19" r:id="rId38" display="https://fbref.com/en/players/8e6d2fcd/Senne-Lammens" xr:uid="{E8A5331D-E924-46B5-9A9A-D5994D1E0473}"/>
-    <hyperlink ref="B18" r:id="rId39" display="https://fbref.com/en/country/NED/Netherlands-Football" xr:uid="{E6D2804C-51EA-4F84-A148-E8A4780846FF}"/>
-    <hyperlink ref="A18" r:id="rId40" display="https://fbref.com/en/players/6b6c793c/Tyrell-Malacia" xr:uid="{20451E5D-69C1-4649-93AE-7D7C5C3B7D93}"/>
-    <hyperlink ref="B17" r:id="rId41" display="https://fbref.com/en/country/POR/Portugal-Football" xr:uid="{C3366E53-3735-45B9-AE6F-B8E93D664219}"/>
-    <hyperlink ref="A17" r:id="rId42" display="https://fbref.com/en/players/d9565625/Diogo-Dalot" xr:uid="{3464CF0F-982C-472C-962B-E5E197AF7B5D}"/>
-    <hyperlink ref="B16" r:id="rId43" display="https://fbref.com/en/country/NED/Netherlands-Football" xr:uid="{6178CF0D-DB44-46C0-810F-0FF8BCC130AA}"/>
-    <hyperlink ref="A16" r:id="rId44" display="https://fbref.com/en/players/028e70b9/Joshua-Zirkzee" xr:uid="{17850C2E-D843-4CF9-B815-18C177C32001}"/>
-    <hyperlink ref="B15" r:id="rId45" display="https://fbref.com/en/country/FRA/France-Football" xr:uid="{35CFEBF2-774E-467C-B908-4123AEC87B5B}"/>
-    <hyperlink ref="A15" r:id="rId46" display="https://fbref.com/en/players/6763f716/Leny-Yoro" xr:uid="{458697AF-7171-476B-B387-0290CDA19F8F}"/>
-    <hyperlink ref="B14" r:id="rId47" display="https://fbref.com/en/country/URU/Uruguay-Football" xr:uid="{B48E6B16-BE10-4331-8650-8CDA2F4EB1EA}"/>
-    <hyperlink ref="A14" r:id="rId48" display="https://fbref.com/en/players/c9817014/Manuel-Ugarte" xr:uid="{CFC35197-F296-4E3E-BB8B-E8964203EE70}"/>
-    <hyperlink ref="B13" r:id="rId49" display="https://fbref.com/en/country/CIV/Cote-dIvoire-Football" xr:uid="{9EDBB871-5A0A-4D03-9C45-4C75198EE66A}"/>
-    <hyperlink ref="A13" r:id="rId50" display="https://fbref.com/en/players/9dc96f10/Amad-Diallo" xr:uid="{EFADC70B-1C24-4015-9A50-B1DA13F10168}"/>
-    <hyperlink ref="B12" r:id="rId51" display="https://fbref.com/en/country/ARG/Argentina-Football" xr:uid="{5BA127E7-F28F-4A67-96F0-6EC2EA847D83}"/>
-    <hyperlink ref="A12" r:id="rId52" display="https://fbref.com/en/players/bac46a10/Lisandro-Martinez" xr:uid="{0C4EDFF4-7BD7-4DB6-8231-CBA4248E0DF9}"/>
-    <hyperlink ref="B11" r:id="rId53" display="https://fbref.com/en/country/MAR/Morocco-Football" xr:uid="{4952C7C2-CAD1-4667-A3DC-EB96F5B40163}"/>
-    <hyperlink ref="A11" r:id="rId54" display="https://fbref.com/en/players/b74277a0/Noussair-Mazraoui" xr:uid="{E822B210-2078-4C84-8CD3-2AF966101AB0}"/>
-    <hyperlink ref="B10" r:id="rId55" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{0A217F0A-EB6E-4875-93BD-2E7C80096315}"/>
-    <hyperlink ref="A10" r:id="rId56" display="https://fbref.com/en/players/9c94165b/Luke-Shaw" xr:uid="{97205F3C-9EEE-4D57-8567-D0ECF06FD994}"/>
-    <hyperlink ref="B9" r:id="rId57" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{F2D85BC7-6D63-44EC-9258-6E7972CB8380}"/>
-    <hyperlink ref="A9" r:id="rId58" display="https://fbref.com/en/players/9674002f/Mason-Mount" xr:uid="{FF4B88D8-EC42-4BE9-B86F-F36DC6AE7A43}"/>
+    <hyperlink ref="B40" r:id="rId1" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{3F72A3A5-56D5-4954-A3B6-79E42E30285A}"/>
+    <hyperlink ref="A40" r:id="rId2" display="https://fbref.com/en/players/4f9091bc/Toby-Collyer" xr:uid="{A49984C9-035D-4ED7-BFF6-BFE428753D7F}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://fbref.com/en/country/CMR/Cameroon-Football" xr:uid="{496DBF89-955E-4872-BCBA-F5EE8E0CFA31}"/>
+    <hyperlink ref="A4" r:id="rId4" display="https://fbref.com/en/players/e9c0c1b2/Andre-Onana" xr:uid="{B0DC6747-5F67-4934-9613-EFFC5261C988}"/>
+    <hyperlink ref="B30" r:id="rId5" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{18F8EE63-3D84-444A-A684-F2A4B8F452AD}"/>
+    <hyperlink ref="A30" r:id="rId6" display="https://fbref.com/en/players/a1d5bd30/Marcus-Rashford" xr:uid="{4387A829-7F2B-4395-94F1-47D9693B53CF}"/>
+    <hyperlink ref="B19" r:id="rId7" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{A7EA4D34-C7D8-4C15-86F7-4E2B6F7ED264}"/>
+    <hyperlink ref="A19" r:id="rId8" display="https://fbref.com/en/players/7b47100c/Harry-Amass" xr:uid="{16EC9CB6-7073-4E09-9636-60F62D7A7595}"/>
+    <hyperlink ref="B39" r:id="rId9" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{DCE8B9BB-FE67-450A-83BD-1A97C48E6EE7}"/>
+    <hyperlink ref="A39" r:id="rId10" display="https://fbref.com/en/players/bd44b52f/Sonny-Aljofree" xr:uid="{2E48A29F-E35A-4703-B9FD-975687D6CFB7}"/>
+    <hyperlink ref="B17" r:id="rId11" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{69C9EBA4-D0BB-44AC-82D3-709623309A9C}"/>
+    <hyperlink ref="A17" r:id="rId12" display="https://fbref.com/en/players/d8b9fc76/Ethan-Williams" xr:uid="{DA7EF6BC-C7AC-4146-B1B8-6AE08787FC89}"/>
+    <hyperlink ref="B15" r:id="rId13" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{5F48DF20-2424-4775-ADE4-2B30EB0DAE10}"/>
+    <hyperlink ref="A15" r:id="rId14" display="https://fbref.com/en/players/143c022e/Ethan-Ennis" xr:uid="{4D8969FB-1D99-4603-B985-E5D207499BFD}"/>
+    <hyperlink ref="B11" r:id="rId15" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{DC2E306B-DEC4-48E9-BBF1-723524E42336}"/>
+    <hyperlink ref="A11" r:id="rId16" display="https://fbref.com/en/players/861e9b3b/Daniel-Gore" xr:uid="{CB57EFD9-7A1C-41EF-A987-F9FB26B92EFE}"/>
+    <hyperlink ref="B23" r:id="rId17" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{7C586973-16AD-4C72-9884-57741421A443}"/>
+    <hyperlink ref="A23" r:id="rId18" display="https://fbref.com/en/players/49134eb2/Joe-Hugill" xr:uid="{3C942A50-F930-4DD0-8A46-0C2E809C2F0F}"/>
+    <hyperlink ref="B16" r:id="rId19" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{012BBF0E-852F-4F07-B5FE-E5F4F9A01540}"/>
+    <hyperlink ref="A16" r:id="rId20" display="https://fbref.com/en/players/5c368c88/Ethan-Wheatley" xr:uid="{719D3E7A-0F8B-40B8-A619-322E65470979}"/>
+    <hyperlink ref="B5" r:id="rId21" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{B74F1AB9-E89D-4E44-963E-E84DFF3C72BD}"/>
+    <hyperlink ref="A5" r:id="rId22" display="https://fbref.com/en/players/64e17fab/Ayden-Heaven" xr:uid="{3D62F65F-9B0E-48B1-8DDE-47E8DC4D5CEA}"/>
+    <hyperlink ref="B12" r:id="rId23" display="https://fbref.com/en/country/PAR/Paraguay-Football" xr:uid="{BD610C72-90D7-40EB-BA7B-F74E512D8055}"/>
+    <hyperlink ref="A12" r:id="rId24" display="https://fbref.com/en/players/69ea448b/Diego-Leon" xr:uid="{34675B85-5D48-4A26-8D69-43557513254D}"/>
+    <hyperlink ref="B25" r:id="rId25" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{101CC625-E8F0-4A2B-BFC2-428D67523A16}"/>
+    <hyperlink ref="A25" r:id="rId26" display="https://fbref.com/en/players/c6220452/Kobbie-Mainoo" xr:uid="{900AD290-779C-4561-B227-678075E6BE40}"/>
+    <hyperlink ref="B42" r:id="rId27" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{DB680947-0EAF-45F3-9672-5D601742FD66}"/>
+    <hyperlink ref="A42" r:id="rId28" display="https://fbref.com/en/players/58630379/Tyler-Fredricson" xr:uid="{5AB50ECA-C52B-40B8-A4BF-DA7132708977}"/>
+    <hyperlink ref="B2" r:id="rId29" display="https://fbref.com/en/country/TUR/Turkey-Football" xr:uid="{A8C90F14-F1C0-4BAC-9340-B609C66F83B2}"/>
+    <hyperlink ref="A2" r:id="rId30" display="https://fbref.com/en/players/072e68ed/Altay-Bayindir" xr:uid="{72C7336C-0146-4005-894A-1F89BE49A78C}"/>
+    <hyperlink ref="B35" r:id="rId31" display="https://fbref.com/en/country/DEN/Denmark-Football" xr:uid="{47496AF9-C9F4-4992-9A46-7155209E3CE2}"/>
+    <hyperlink ref="A35" r:id="rId32" display="https://fbref.com/en/players/e6536124/Patrick-Dorgu" xr:uid="{B2CC8187-60D3-409C-82D0-E3E7E78A4906}"/>
+    <hyperlink ref="B41" r:id="rId33" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{7276AEB2-71E9-42BF-8FB5-BB2020CBE4DC}"/>
+    <hyperlink ref="A41" r:id="rId34" display="https://fbref.com/en/players/a6de6361/Tom-Heaton" xr:uid="{C2F55E8B-E7DB-449C-BE43-4E78713600E0}"/>
+    <hyperlink ref="B22" r:id="rId35" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{87ACC8BC-A024-4CBE-9E17-DC7148F7015B}"/>
+    <hyperlink ref="A22" r:id="rId36" display="https://fbref.com/en/players/dbf053da/Jadon-Sancho" xr:uid="{3833287A-E4EB-4527-9D74-09662B51D4CD}"/>
+    <hyperlink ref="B38" r:id="rId37" display="https://fbref.com/en/country/BEL/Belgium-Football" xr:uid="{0F4D7669-FF1D-42E1-914C-43726D0939FA}"/>
+    <hyperlink ref="A38" r:id="rId38" display="https://fbref.com/en/players/8e6d2fcd/Senne-Lammens" xr:uid="{E8A5331D-E924-46B5-9A9A-D5994D1E0473}"/>
+    <hyperlink ref="B43" r:id="rId39" display="https://fbref.com/en/country/NED/Netherlands-Football" xr:uid="{E6D2804C-51EA-4F84-A148-E8A4780846FF}"/>
+    <hyperlink ref="A43" r:id="rId40" display="https://fbref.com/en/players/6b6c793c/Tyrell-Malacia" xr:uid="{20451E5D-69C1-4649-93AE-7D7C5C3B7D93}"/>
+    <hyperlink ref="B13" r:id="rId41" display="https://fbref.com/en/country/POR/Portugal-Football" xr:uid="{C3366E53-3735-45B9-AE6F-B8E93D664219}"/>
+    <hyperlink ref="A13" r:id="rId42" display="https://fbref.com/en/players/d9565625/Diogo-Dalot" xr:uid="{3464CF0F-982C-472C-962B-E5E197AF7B5D}"/>
+    <hyperlink ref="B24" r:id="rId43" display="https://fbref.com/en/country/NED/Netherlands-Football" xr:uid="{6178CF0D-DB44-46C0-810F-0FF8BCC130AA}"/>
+    <hyperlink ref="A24" r:id="rId44" display="https://fbref.com/en/players/028e70b9/Joshua-Zirkzee" xr:uid="{17850C2E-D843-4CF9-B815-18C177C32001}"/>
+    <hyperlink ref="B26" r:id="rId45" display="https://fbref.com/en/country/FRA/France-Football" xr:uid="{35CFEBF2-774E-467C-B908-4123AEC87B5B}"/>
+    <hyperlink ref="A26" r:id="rId46" display="https://fbref.com/en/players/6763f716/Leny-Yoro" xr:uid="{458697AF-7171-476B-B387-0290CDA19F8F}"/>
+    <hyperlink ref="B29" r:id="rId47" display="https://fbref.com/en/country/URU/Uruguay-Football" xr:uid="{B48E6B16-BE10-4331-8650-8CDA2F4EB1EA}"/>
+    <hyperlink ref="A29" r:id="rId48" display="https://fbref.com/en/players/c9817014/Manuel-Ugarte" xr:uid="{CFC35197-F296-4E3E-BB8B-E8964203EE70}"/>
+    <hyperlink ref="B3" r:id="rId49" display="https://fbref.com/en/country/CIV/Cote-dIvoire-Football" xr:uid="{9EDBB871-5A0A-4D03-9C45-4C75198EE66A}"/>
+    <hyperlink ref="A3" r:id="rId50" display="https://fbref.com/en/players/9dc96f10/Amad-Diallo" xr:uid="{EFADC70B-1C24-4015-9A50-B1DA13F10168}"/>
+    <hyperlink ref="B27" r:id="rId51" display="https://fbref.com/en/country/ARG/Argentina-Football" xr:uid="{5BA127E7-F28F-4A67-96F0-6EC2EA847D83}"/>
+    <hyperlink ref="A27" r:id="rId52" display="https://fbref.com/en/players/bac46a10/Lisandro-Martinez" xr:uid="{0C4EDFF4-7BD7-4DB6-8231-CBA4248E0DF9}"/>
+    <hyperlink ref="B34" r:id="rId53" display="https://fbref.com/en/country/MAR/Morocco-Football" xr:uid="{4952C7C2-CAD1-4667-A3DC-EB96F5B40163}"/>
+    <hyperlink ref="A34" r:id="rId54" display="https://fbref.com/en/players/b74277a0/Noussair-Mazraoui" xr:uid="{E822B210-2078-4C84-8CD3-2AF966101AB0}"/>
+    <hyperlink ref="B28" r:id="rId55" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{0A217F0A-EB6E-4875-93BD-2E7C80096315}"/>
+    <hyperlink ref="A28" r:id="rId56" display="https://fbref.com/en/players/9c94165b/Luke-Shaw" xr:uid="{97205F3C-9EEE-4D57-8567-D0ECF06FD994}"/>
+    <hyperlink ref="B31" r:id="rId57" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{F2D85BC7-6D63-44EC-9258-6E7972CB8380}"/>
+    <hyperlink ref="A31" r:id="rId58" display="https://fbref.com/en/players/9674002f/Mason-Mount" xr:uid="{FF4B88D8-EC42-4BE9-B86F-F36DC6AE7A43}"/>
     <hyperlink ref="B8" r:id="rId59" display="https://fbref.com/en/country/CMR/Cameroon-Football" xr:uid="{22AA091C-7B4C-4E2A-9015-78D7A114E142}"/>
     <hyperlink ref="A8" r:id="rId60" display="https://fbref.com/en/players/6afaebf2/Bryan-Mbeumo" xr:uid="{0E57A101-04A9-45D2-9E5A-9248B1B2FCF9}"/>
-    <hyperlink ref="B7" r:id="rId61" display="https://fbref.com/en/country/SVN/Slovenia-Football" xr:uid="{2C693497-12EA-4647-A4C2-622851AD62B3}"/>
-    <hyperlink ref="A7" r:id="rId62" display="https://fbref.com/en/players/3260690c/Benjamin-Sesko" xr:uid="{B45285C0-B831-4F52-84DA-298AF2E3ADA8}"/>
-    <hyperlink ref="B6" r:id="rId63" display="https://fbref.com/en/country/BRA/Brazil-Football" xr:uid="{122A0A60-8CD2-4EE0-AF47-C5E8D5406C63}"/>
-    <hyperlink ref="A6" r:id="rId64" display="https://fbref.com/en/players/dc62b55d/Matheus-Cunha" xr:uid="{32DB579E-5B3F-446C-A668-FCE26FAE9E0D}"/>
-    <hyperlink ref="B5" r:id="rId65" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{434E7E76-06D9-4A5D-85B8-B269E29C49FF}"/>
-    <hyperlink ref="A5" r:id="rId66" display="https://fbref.com/en/players/d8931174/Harry-Maguire" xr:uid="{75EE90AF-9424-449F-8D59-37913CC93609}"/>
-    <hyperlink ref="B4" r:id="rId67" display="https://fbref.com/en/country/NED/Netherlands-Football" xr:uid="{04D8C9C4-8118-4EBF-812A-89B5C7EF1BC6}"/>
-    <hyperlink ref="A4" r:id="rId68" display="https://fbref.com/en/players/d6e53a3a/Matthijs-de-Ligt" xr:uid="{EB78D56D-FE1F-4030-A1B7-6E354143C7BC}"/>
-    <hyperlink ref="B3" r:id="rId69" display="https://fbref.com/en/country/POR/Portugal-Football" xr:uid="{ED031C1B-D846-4AAB-A333-2661385A20A8}"/>
-    <hyperlink ref="A3" r:id="rId70" display="https://fbref.com/en/players/507c7bdf/Bruno-Fernandes" xr:uid="{2CECD760-2A6D-40AB-9CBB-D36454EA7B2A}"/>
-    <hyperlink ref="B2" r:id="rId71" display="https://fbref.com/en/country/BRA/Brazil-Football" xr:uid="{E0C0A4D5-70CE-4FBE-A2BF-C6690993FE2F}"/>
-    <hyperlink ref="A2" r:id="rId72" display="https://fbref.com/en/players/4d224fe8/Casemiro" xr:uid="{567272C0-CF25-4620-A5CA-0B7781BCA890}"/>
+    <hyperlink ref="B6" r:id="rId61" display="https://fbref.com/en/country/SVN/Slovenia-Football" xr:uid="{2C693497-12EA-4647-A4C2-622851AD62B3}"/>
+    <hyperlink ref="A6" r:id="rId62" display="https://fbref.com/en/players/3260690c/Benjamin-Sesko" xr:uid="{B45285C0-B831-4F52-84DA-298AF2E3ADA8}"/>
+    <hyperlink ref="B32" r:id="rId63" display="https://fbref.com/en/country/BRA/Brazil-Football" xr:uid="{122A0A60-8CD2-4EE0-AF47-C5E8D5406C63}"/>
+    <hyperlink ref="A32" r:id="rId64" display="https://fbref.com/en/players/dc62b55d/Matheus-Cunha" xr:uid="{32DB579E-5B3F-446C-A668-FCE26FAE9E0D}"/>
+    <hyperlink ref="B20" r:id="rId65" display="https://fbref.com/en/country/ENG/England-Football" xr:uid="{434E7E76-06D9-4A5D-85B8-B269E29C49FF}"/>
+    <hyperlink ref="A20" r:id="rId66" display="https://fbref.com/en/players/d8931174/Harry-Maguire" xr:uid="{75EE90AF-9424-449F-8D59-37913CC93609}"/>
+    <hyperlink ref="B33" r:id="rId67" display="https://fbref.com/en/country/NED/Netherlands-Football" xr:uid="{04D8C9C4-8118-4EBF-812A-89B5C7EF1BC6}"/>
+    <hyperlink ref="A33" r:id="rId68" display="https://fbref.com/en/players/d6e53a3a/Matthijs-de-Ligt" xr:uid="{EB78D56D-FE1F-4030-A1B7-6E354143C7BC}"/>
+    <hyperlink ref="B7" r:id="rId69" display="https://fbref.com/en/country/POR/Portugal-Football" xr:uid="{ED031C1B-D846-4AAB-A333-2661385A20A8}"/>
+    <hyperlink ref="A7" r:id="rId70" display="https://fbref.com/en/players/507c7bdf/Bruno-Fernandes" xr:uid="{2CECD760-2A6D-40AB-9CBB-D36454EA7B2A}"/>
+    <hyperlink ref="B9" r:id="rId71" display="https://fbref.com/en/country/BRA/Brazil-Football" xr:uid="{E0C0A4D5-70CE-4FBE-A2BF-C6690993FE2F}"/>
+    <hyperlink ref="A9" r:id="rId72" display="https://fbref.com/en/players/4d224fe8/Casemiro" xr:uid="{567272C0-CF25-4620-A5CA-0B7781BCA890}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
